--- a/test/fixtures/products-import-valid.xlsx
+++ b/test/fixtures/products-import-valid.xlsx
@@ -34,6 +34,9 @@
     <t>category</t>
   </si>
   <si>
+    <t>subcategory</t>
+  </si>
+  <si>
     <t>rating</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>STATIONERY</t>
   </si>
   <si>
+    <t>WRITING_INSTRUMENTS</t>
+  </si>
+  <si>
     <t>https://example.com/img/desk-organizer.png</t>
   </si>
   <si>
@@ -67,6 +73,9 @@
     <t>SPORTS</t>
   </si>
   <si>
+    <t>FITNESS</t>
+  </si>
+  <si>
     <t>https://example.com/img/resistance-bands.png</t>
   </si>
   <si>
@@ -80,6 +89,9 @@
   </si>
   <si>
     <t>ELECTRONICS</t>
+  </si>
+  <si>
+    <t>LAPTOPS</t>
   </si>
   <si>
     <t>https://example.com/img/usb-c-hub.png</t>
@@ -147,83 +159,95 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>24.5</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="H2" t="s">
-        <v>12</v>
+      <c r="I2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>19.99</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>120</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3">
         <v>5</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
+      <c r="I3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="H4" t="s">
-        <v>22</v>
+      <c r="I4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
